--- a/1.training_model/slide_presentation/Plan Execution - Device Identifier.xlsx
+++ b/1.training_model/slide_presentation/Plan Execution - Device Identifier.xlsx
@@ -826,10 +826,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2339,6 +2335,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="fb6e3268-d223-4590-a8af-21a0073b32ab" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003228A6EDEA2CA3459F2BF5FF0B1ACE32" ma:contentTypeVersion="5" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f63bff5a8cbd78bc11808b163a9718e2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="fb6e3268-d223-4590-a8af-21a0073b32ab" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b1dcc29a541218455dd5cbe6745da577" ns3:_="">
     <xsd:import namespace="fb6e3268-d223-4590-a8af-21a0073b32ab"/>
@@ -2488,14 +2492,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="fb6e3268-d223-4590-a8af-21a0073b32ab" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -2506,6 +2502,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28F07F0D-FD61-4764-B10C-FC94F2C04ED4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="fb6e3268-d223-4590-a8af-21a0073b32ab"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7FE2514C-B0F1-4000-843B-E133E9E2F9B4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2523,22 +2535,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{28F07F0D-FD61-4764-B10C-FC94F2C04ED4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="fb6e3268-d223-4590-a8af-21a0073b32ab"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E87AA5CD-D972-4497-AF21-46D0DC4756CD}">
   <ds:schemaRefs>
